--- a/data/raw/benv_exports/salmonellosi_2026_italia.xlsx
+++ b/data/raw/benv_exports/salmonellosi_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,37 +484,37 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>83422</v>
+        <v>85652</v>
       </c>
       <c r="B4" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C4" t="str">
         <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>20/02/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>12/02/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>13/03/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H4" t="str">
-        <v>BOVINO</v>
+        <v>SUINO</v>
       </c>
       <c r="I4" t="str">
-        <v>MONTICHIARI</v>
+        <v>MANCIANO</v>
       </c>
       <c r="J4" t="str">
-        <v>BS</v>
+        <v>GR</v>
       </c>
       <c r="K4" t="str">
-        <v>LOMBARDIA</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="5">
@@ -554,42 +554,42 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>83833</v>
+        <v>83422</v>
       </c>
       <c r="B6" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C6" t="str">
         <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>07/04/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>19/03/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>20/05/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="G6" t="str">
         <v>TYPHIMURIUM</v>
       </c>
       <c r="H6" t="str">
-        <v>BUFALO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I6" t="str">
-        <v>SAN TAMMARO</v>
+        <v>MONTICHIARI</v>
       </c>
       <c r="J6" t="str">
-        <v>CE</v>
+        <v>BS</v>
       </c>
       <c r="K6" t="str">
-        <v>CAMPANIA</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>82920</v>
+        <v>83833</v>
       </c>
       <c r="B7" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -598,33 +598,33 @@
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>28/01/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>15/01/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>04/03/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>DUBLIN</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H7" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I7" t="str">
-        <v>VILLAFRANCA DI VERONA</v>
+        <v>SAN TAMMARO</v>
       </c>
       <c r="J7" t="str">
-        <v>VR</v>
+        <v>CE</v>
       </c>
       <c r="K7" t="str">
-        <v>VENETO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>82869</v>
+        <v>82920</v>
       </c>
       <c r="B8" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -633,68 +633,68 @@
         <v>E</v>
       </c>
       <c r="D8" t="str">
-        <v>21/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>14/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>27/02/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>DUBLIN</v>
       </c>
       <c r="H8" t="str">
-        <v>GALLUS GALLUS</v>
+        <v>BOVINO</v>
       </c>
       <c r="I8" t="str">
-        <v>PICINISCO</v>
+        <v>VILLAFRANCA DI VERONA</v>
       </c>
       <c r="J8" t="str">
-        <v>FR</v>
+        <v>VR</v>
       </c>
       <c r="K8" t="str">
-        <v>LAZIO</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>83084</v>
+        <v>82869</v>
       </c>
       <c r="B9" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C9" t="str">
         <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>23/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>23/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>12/03/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="G9" t="str">
         <v>TYPHIMURIUM</v>
       </c>
       <c r="H9" t="str">
-        <v>OVINO</v>
+        <v>GALLUS GALLUS</v>
       </c>
       <c r="I9" t="str">
-        <v>SANTA GIUSTA</v>
+        <v>PICINISCO</v>
       </c>
       <c r="J9" t="str">
-        <v>OR</v>
+        <v>FR</v>
       </c>
       <c r="K9" t="str">
-        <v>SARDEGNA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>83013</v>
+        <v>83084</v>
       </c>
       <c r="B10" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -703,103 +703,103 @@
         <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>15/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>12/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>21/04/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="G10" t="str">
         <v>TYPHIMURIUM</v>
       </c>
       <c r="H10" t="str">
-        <v>BOVINO</v>
+        <v>OVINO</v>
       </c>
       <c r="I10" t="str">
-        <v>ANZIO</v>
+        <v>SANTA GIUSTA</v>
       </c>
       <c r="J10" t="str">
-        <v>RM</v>
+        <v>OR</v>
       </c>
       <c r="K10" t="str">
-        <v>LAZIO</v>
+        <v>SARDEGNA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>83702</v>
+        <v>83013</v>
       </c>
       <c r="B11" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C11" t="str">
         <v>E</v>
       </c>
       <c r="D11" t="str">
-        <v>12/03/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>10/03/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>12/03/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H11" t="str">
-        <v>GALLUS GALLUS</v>
+        <v>BOVINO</v>
       </c>
       <c r="I11" t="str">
-        <v>VICENZA</v>
+        <v>ANZIO</v>
       </c>
       <c r="J11" t="str">
-        <v>VI</v>
+        <v>RM</v>
       </c>
       <c r="K11" t="str">
-        <v>VENETO</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>83475</v>
+        <v>83702</v>
       </c>
       <c r="B12" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C12" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D12" t="str">
-        <v>20/03/2026</v>
+        <v>12/03/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>18/02/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>-</v>
+        <v>12/03/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H12" t="str">
-        <v>BUFALO</v>
+        <v>GALLUS GALLUS</v>
       </c>
       <c r="I12" t="str">
-        <v>CAPACCIO</v>
+        <v>VICENZA</v>
       </c>
       <c r="J12" t="str">
-        <v>SA</v>
+        <v>VI</v>
       </c>
       <c r="K12" t="str">
-        <v>CAMPANIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>85362</v>
+        <v>83475</v>
       </c>
       <c r="B13" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -808,10 +808,10 @@
         <v>C</v>
       </c>
       <c r="D13" t="str">
-        <v>26/06/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>16/06/2026</v>
+        <v>18/02/2026</v>
       </c>
       <c r="F13" t="str">
         <v>-</v>
@@ -820,33 +820,33 @@
         <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H13" t="str">
-        <v>GALLUS GALLUS</v>
+        <v>BUFALO</v>
       </c>
       <c r="I13" t="str">
-        <v>CAVOUR</v>
+        <v>CAPACCIO</v>
       </c>
       <c r="J13" t="str">
-        <v>TO</v>
+        <v>SA</v>
       </c>
       <c r="K13" t="str">
-        <v>PIEMONTE</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>84021</v>
+        <v>85362</v>
       </c>
       <c r="B14" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C14" t="str">
         <v>C</v>
       </c>
       <c r="D14" t="str">
-        <v>14/04/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>31/03/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="F14" t="str">
         <v>-</v>
@@ -855,103 +855,103 @@
         <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H14" t="str">
-        <v>BUFALO</v>
+        <v>GALLUS GALLUS</v>
       </c>
       <c r="I14" t="str">
-        <v>VAIRANO PATENORA</v>
+        <v>CAVOUR</v>
       </c>
       <c r="J14" t="str">
-        <v>CE</v>
+        <v>TO</v>
       </c>
       <c r="K14" t="str">
-        <v>CAMPANIA</v>
+        <v>PIEMONTE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>85289</v>
+        <v>85609</v>
       </c>
       <c r="B15" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C15" t="str">
         <v>C</v>
       </c>
       <c r="D15" t="str">
-        <v>23/06/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>23/06/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
       </c>
       <c r="G15" t="str">
-        <v>DUBLIN</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H15" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I15" t="str">
-        <v>NEGRAR DI VALPOLICELLA</v>
+        <v>OSIO SOPRA</v>
       </c>
       <c r="J15" t="str">
-        <v>VR</v>
+        <v>BG</v>
       </c>
       <c r="K15" t="str">
-        <v>VENETO</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>85063</v>
+        <v>85912</v>
       </c>
       <c r="B16" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C16" t="str">
         <v>C</v>
       </c>
       <c r="D16" t="str">
-        <v>19/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>08/06/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="F16" t="str">
         <v>-</v>
       </c>
       <c r="G16" t="str">
-        <v>Sconosciuto</v>
+        <v>STANLEY</v>
       </c>
       <c r="H16" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I16" t="str">
-        <v>VETRALLA</v>
+        <v>AGROPOLI</v>
       </c>
       <c r="J16" t="str">
-        <v>VT</v>
+        <v>SA</v>
       </c>
       <c r="K16" t="str">
-        <v>LAZIO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>84939</v>
+        <v>84021</v>
       </c>
       <c r="B17" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C17" t="str">
         <v>C</v>
       </c>
       <c r="D17" t="str">
-        <v>04/06/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>19/05/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
@@ -963,18 +963,193 @@
         <v>BUFALO</v>
       </c>
       <c r="I17" t="str">
-        <v>CAPACCIO</v>
+        <v>VAIRANO PATENORA</v>
       </c>
       <c r="J17" t="str">
-        <v>SA</v>
+        <v>CE</v>
       </c>
       <c r="K17" t="str">
         <v>CAMPANIA</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>85720</v>
+      </c>
+      <c r="B18" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C18" t="str">
+        <v>C</v>
+      </c>
+      <c r="D18" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E18" t="str">
+        <v>02/07/2026</v>
+      </c>
+      <c r="F18" t="str">
+        <v>-</v>
+      </c>
+      <c r="G18" t="str">
+        <v>SENFTENBERG</v>
+      </c>
+      <c r="H18" t="str">
+        <v>BUFALO</v>
+      </c>
+      <c r="I18" t="str">
+        <v>EBOLI</v>
+      </c>
+      <c r="J18" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K18" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>85289</v>
+      </c>
+      <c r="B19" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C19" t="str">
+        <v>C</v>
+      </c>
+      <c r="D19" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="E19" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="F19" t="str">
+        <v>-</v>
+      </c>
+      <c r="G19" t="str">
+        <v>DUBLIN</v>
+      </c>
+      <c r="H19" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I19" t="str">
+        <v>NEGRAR DI VALPOLICELLA</v>
+      </c>
+      <c r="J19" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K19" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>85721</v>
+      </c>
+      <c r="B20" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C20" t="str">
+        <v>C</v>
+      </c>
+      <c r="D20" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E20" t="str">
+        <v>02/07/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>-</v>
+      </c>
+      <c r="G20" t="str">
+        <v>STANLEY</v>
+      </c>
+      <c r="H20" t="str">
+        <v>BUFALO</v>
+      </c>
+      <c r="I20" t="str">
+        <v>EBOLI</v>
+      </c>
+      <c r="J20" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K20" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>85063</v>
+      </c>
+      <c r="B21" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C21" t="str">
+        <v>C</v>
+      </c>
+      <c r="D21" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="E21" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>-</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Sconosciuto</v>
+      </c>
+      <c r="H21" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I21" t="str">
+        <v>VETRALLA</v>
+      </c>
+      <c r="J21" t="str">
+        <v>VT</v>
+      </c>
+      <c r="K21" t="str">
+        <v>LAZIO</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>84939</v>
+      </c>
+      <c r="B22" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C22" t="str">
+        <v>C</v>
+      </c>
+      <c r="D22" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="E22" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="F22" t="str">
+        <v>-</v>
+      </c>
+      <c r="G22" t="str">
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+      </c>
+      <c r="H22" t="str">
+        <v>BUFALO</v>
+      </c>
+      <c r="I22" t="str">
+        <v>CAPACCIO</v>
+      </c>
+      <c r="J22" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K22" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>